--- a/tia_exports/PLCTags.xlsx
+++ b/tia_exports/PLCTags.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Constants" sheetId="1" r:id="R5d5ef1ec6336432a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TagTable Properties" sheetId="2" r:id="R0373c5c0c3a447e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Constants" sheetId="1" r:id="R288a46bcced04c62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TagTable Properties" sheetId="2" r:id="R8c5c4fef9c7744b2"/>
   </x:sheets>
 </x:workbook>
 </file>
